--- a/apps/api/assets/vocabulary/初中/人教版/人教版初中英语七年级下册.xlsx
+++ b/apps/api/assets/vocabulary/初中/人教版/人教版初中英语七年级下册.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D537"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -669,6 +669,16 @@
           <t>speak English</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 说英语；讲英语；相信我会讲英文</t>
@@ -732,6 +742,16 @@
           <t>be good at ...</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 善于
@@ -889,6 +909,16 @@
           <t>talk to ...</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 向…谈；〔口语〕申斥
@@ -951,6 +981,16 @@
           <t>play the drums</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -986,6 +1026,16 @@
           <t>play the piano</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 弹钢琴
@@ -1020,6 +1070,16 @@
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>play the violin</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1107,6 +1167,16 @@
           <t>be good with ...</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 擅长；善于和……相处；和……相处的很好</t>
@@ -1144,6 +1214,16 @@
           <t>make friends</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 交朋友；交友；结交朋友</t>
@@ -1180,6 +1260,16 @@
           <t>help with sth.</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 帮助
@@ -1191,6 +1281,16 @@
       <c r="A36" s="2" t="inlineStr">
         <is>
           <t>help sb. with sth.</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1256,6 +1356,16 @@
           <t>on the weekend</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 在周末；在这个周末；美式英语</t>
@@ -1312,6 +1422,16 @@
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Lisa</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1542,6 +1662,16 @@
           <t>take a shower</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 洗个淋浴
@@ -1765,6 +1895,16 @@
           <t>radio station</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 广播电台
@@ -1776,6 +1916,16 @@
       <c r="A63" s="2" t="inlineStr">
         <is>
           <t>o'clock</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -1858,6 +2008,16 @@
       <c r="A67" s="2" t="inlineStr">
         <is>
           <t>on weekends</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -2020,6 +2180,16 @@
           <t>do homework</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 做作业；做家庭作业；做功课</t>
@@ -2030,6 +2200,16 @@
       <c r="A75" s="2" t="inlineStr">
         <is>
           <t>do one's homework</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -2122,6 +2302,16 @@
           <t>take a walk</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 散步
@@ -2180,6 +2370,16 @@
       <c r="A82" s="2" t="inlineStr">
         <is>
           <t>either ... or ...</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -2222,6 +2422,16 @@
           <t>lots of</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">adj. 许多；很多
@@ -2396,6 +2606,16 @@
           <t>get to</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 接触到；开始；〈美口〉收买
@@ -2477,6 +2697,16 @@
       <c r="A96" s="2" t="inlineStr">
         <is>
           <t>take the subway</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -2540,6 +2770,16 @@
           <t>ride a bike</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 骑自行车；骑车；骑单车</t>
@@ -2810,6 +3050,16 @@
           <t>every day</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 每日
@@ -2844,6 +3094,16 @@
       <c r="A113" s="2" t="inlineStr">
         <is>
           <t>by bike</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -2952,6 +3212,16 @@
       <c r="A118" s="2" t="inlineStr">
         <is>
           <t>think of</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -3082,6 +3352,16 @@
       <c r="A124" s="2" t="inlineStr">
         <is>
           <t>between ... and ...</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -3357,6 +3637,16 @@
           <t>Dave</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
           <t>n. 戴夫（男子名）</t>
@@ -3440,6 +3730,16 @@
           <t>be on time</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 要准时；守时；准时到达</t>
@@ -3541,6 +3841,16 @@
       <c r="A145" s="2" t="inlineStr">
         <is>
           <t>listen to ...</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -3795,6 +4105,16 @@
           <t>go out</t>
         </is>
       </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 出去；灭；辞职；下台
@@ -3856,6 +4176,16 @@
           <t>do the dishes</t>
         </is>
       </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 洗碗碟
@@ -3891,6 +4221,16 @@
       <c r="A161" s="2" t="inlineStr">
         <is>
           <t>make one's bed</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -4119,6 +4459,16 @@
           <t>be strict</t>
         </is>
       </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 严格；严厉；是严格的</t>
@@ -4129,6 +4479,16 @@
       <c r="A172" s="2" t="inlineStr">
         <is>
           <t>be strict with sb.</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -4188,6 +4548,16 @@
       <c r="A175" s="2" t="inlineStr">
         <is>
           <t>follow the rules</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -4299,6 +4669,16 @@
           <t>Clark</t>
         </is>
       </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 克拉克（男子名）
@@ -4354,6 +4734,16 @@
       <c r="A183" s="2" t="inlineStr">
         <is>
           <t>New York</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -4689,6 +5079,16 @@
           <t>kind of</t>
         </is>
       </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 有点儿；有几分
@@ -4769,6 +5169,16 @@
       <c r="A202" s="2" t="inlineStr">
         <is>
           <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -5024,6 +5434,16 @@
           <t>get lost</t>
         </is>
       </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">int. 〈口〉滚开；别烦我
@@ -5111,6 +5531,16 @@
           <t>be in danger</t>
         </is>
       </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 处于危险之中；处于危险中；处于危险当中</t>
@@ -5121,6 +5551,16 @@
       <c r="A218" s="2" t="inlineStr">
         <is>
           <t>be in great danger</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -5312,6 +5752,16 @@
           <t>made of</t>
         </is>
       </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. “make certain”的变体
@@ -5325,6 +5775,16 @@
           <t>be made of</t>
         </is>
       </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. …制的
@@ -5336,6 +5796,16 @@
       <c r="A228" s="2" t="inlineStr">
         <is>
           <t>Julie</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -5441,6 +5911,16 @@
           <t>read a newspaper</t>
         </is>
       </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -5501,6 +5981,16 @@
           <t>make soup</t>
         </is>
       </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -5561,6 +6051,16 @@
           <t>go to the movies</t>
         </is>
       </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 去看电影
@@ -5596,6 +6096,16 @@
       <c r="A241" s="2" t="inlineStr">
         <is>
           <t>eat out</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -5685,6 +6195,16 @@
           <t>drink tea</t>
         </is>
       </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 喝茶；饮茶；品茗尝鲜</t>
@@ -5914,6 +6434,16 @@
           <t>the United States</t>
         </is>
       </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 美利坚合众国
@@ -5971,6 +6501,16 @@
       <c r="A258" s="2" t="inlineStr">
         <is>
           <t>Dragon Boat Festival</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
@@ -6203,6 +6743,16 @@
           <t>Steve</t>
         </is>
       </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
           <t>n. 史蒂夫（男子名）</t>
@@ -6476,6 +7026,16 @@
       <c r="A280" s="2" t="inlineStr">
         <is>
           <t>take a message</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
@@ -6564,6 +7124,16 @@
           <t>call back</t>
         </is>
       </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 取消；喊回；回一个电话；再打一个电话来
@@ -6577,6 +7147,16 @@
           <t>call sb. back</t>
         </is>
       </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 取消；喊回；回一个电话；再打一个电话来
@@ -6611,6 +7191,16 @@
       <c r="A287" s="2" t="inlineStr">
         <is>
           <t>right now</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
@@ -6914,6 +7504,16 @@
           <t>on vacation</t>
         </is>
       </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 度假；在度假；在度假中</t>
@@ -6924,6 +7524,16 @@
       <c r="A301" s="2" t="inlineStr">
         <is>
           <t>on a vacation</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
@@ -7541,6 +8151,16 @@
           <t>pay phone</t>
         </is>
       </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 公用自动收费电话亭
@@ -7599,6 +8219,16 @@
       <c r="A331" s="2" t="inlineStr">
         <is>
           <t>across from</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
@@ -7781,6 +8411,16 @@
           <t>go along</t>
         </is>
       </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 前进
@@ -7792,6 +8432,16 @@
       <c r="A340" s="2" t="inlineStr">
         <is>
           <t>go along the street</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
@@ -7883,6 +8533,16 @@
           <t>turn right</t>
         </is>
       </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 转往右面
@@ -7965,6 +8625,16 @@
           <t>spend time</t>
         </is>
       </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 度过时光；花时间；消磨时间</t>
@@ -8166,6 +8836,16 @@
           <t>enjoy reading</t>
         </is>
       </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -8339,6 +9019,16 @@
           <t>of medium height</t>
         </is>
       </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -8349,6 +9039,16 @@
       <c r="A366" s="2" t="inlineStr">
         <is>
           <t>be of medium height</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
@@ -8460,6 +9160,16 @@
       <c r="A371" s="2" t="inlineStr">
         <is>
           <t>a little</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
@@ -9087,6 +9797,16 @@
           <t>in the end</t>
         </is>
       </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 终于
@@ -9171,6 +9891,16 @@
           <t>Dean</t>
         </is>
       </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
           <t>n. 院长；系主任；教务长；主持牧师</t>
@@ -9385,6 +10115,16 @@
           <t>would like</t>
         </is>
       </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 想要
@@ -9469,6 +10209,16 @@
       <c r="A416" s="2" t="inlineStr">
         <is>
           <t>take one's order</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
@@ -9532,6 +10282,16 @@
           <t>one bowl of ...</t>
         </is>
       </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -9542,6 +10302,16 @@
       <c r="A420" s="2" t="inlineStr">
         <is>
           <t>one large bowl of ...</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
@@ -9738,6 +10508,16 @@
           <t>around the world</t>
         </is>
       </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 环球
@@ -9915,6 +10695,16 @@
       <c r="A437" s="2" t="inlineStr">
         <is>
           <t>blow out</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
@@ -9978,6 +10768,16 @@
           <t>the UK</t>
         </is>
       </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
           <t>（等于the United Kingdom）英国</t>
@@ -9988,6 +10788,16 @@
       <c r="A441" s="2" t="inlineStr">
         <is>
           <t>the United Kingdom</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D441" s="2" t="inlineStr">
@@ -10072,6 +10882,16 @@
           <t>get popular</t>
         </is>
       </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -10127,6 +10947,16 @@
       <c r="A448" s="2" t="inlineStr">
         <is>
           <t>bring good luck to ...</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D448" s="2" t="inlineStr">
@@ -10189,6 +11019,16 @@
           <t>milk a cow</t>
         </is>
       </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -10226,6 +11066,16 @@
           <t>ride a horse</t>
         </is>
       </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 骑马；骑一匹马；乘马</t>
@@ -10262,6 +11112,16 @@
           <t>feed chickens</t>
         </is>
       </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -10319,6 +11179,16 @@
           <t>quite a lot</t>
         </is>
       </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 相当多；好些；好多</t>
@@ -10329,6 +11199,16 @@
       <c r="A459" s="2" t="inlineStr">
         <is>
           <t>quite a lot of ...</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D459" s="2" t="inlineStr">
@@ -10483,6 +11363,16 @@
           <t>in the countryside</t>
         </is>
       </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 在乡村；在乡下；在农村</t>
@@ -10657,6 +11547,16 @@
       <c r="A474" s="2" t="inlineStr">
         <is>
           <t>fire station</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D474" s="2" t="inlineStr">
@@ -10910,6 +11810,16 @@
           <t>all in all</t>
         </is>
       </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 全部；完全；第一
@@ -10966,6 +11876,16 @@
       <c r="A488" s="2" t="inlineStr">
         <is>
           <t>be interested in</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D488" s="2" t="inlineStr">
@@ -11312,6 +12232,16 @@
           <t>stay up late</t>
         </is>
       </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 整晚不睡；守着；迟睡
@@ -11345,6 +12275,16 @@
       <c r="A505" s="2" t="inlineStr">
         <is>
           <t>run away</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D505" s="2" t="inlineStr">
@@ -11431,6 +12371,16 @@
       <c r="A509" s="2" t="inlineStr">
         <is>
           <t>shout at ...</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D509" s="2" t="inlineStr">
@@ -11541,6 +12491,16 @@
           <t>fly a kite</t>
         </is>
       </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 放风筝；试探舆论；开空头支票；〈美〉(从狱中)非法寄出信件
@@ -11673,6 +12633,16 @@
           <t>put up</t>
         </is>
       </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
           <t>提供；建造；举起；提高；推举，提名；供给…住宿；直接行动</t>
@@ -11710,6 +12680,16 @@
           <t>each other</t>
         </is>
       </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">pron. 彼此
@@ -11747,6 +12727,16 @@
           <t>get a surprise</t>
         </is>
       </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -11830,6 +12820,16 @@
           <t>shout to ...</t>
         </is>
       </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D528" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 呼唤；对某人大叫；向…喊叫</t>
@@ -11937,6 +12937,16 @@
       <c r="A533" s="2" t="inlineStr">
         <is>
           <t>wake ... up</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D533" s="2" t="inlineStr">
